--- a/outputs/figure_source_data/source_data_fig_3_b.xlsx
+++ b/outputs/figure_source_data/source_data_fig_3_b.xlsx
@@ -4613,7 +4613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4623,9 +4623,11 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4671,10 +4673,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>mas_ks_normality_p</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>human_ks_normality_p</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>significance_label</t>
         </is>
@@ -4708,13 +4720,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.1357611496474826</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+        <v>0.5083149192316914</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.4303021182649574</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.5920249538014427</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -4748,13 +4766,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Wilcoxon signed-rank</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.001500519663478</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+        <v>0.8767797258382193</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.4610363664663331</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.1562858308455812</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
@@ -4788,13 +4812,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Paired t-test</t>
+          <t>Independent-samples Welch t-test</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.2029711680985655</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+        <v>0.6369561475535357</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.6700639720044255</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.5177749602211584</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>n.s.</t>
         </is>
